--- a/data/countypop.xlsx
+++ b/data/countypop.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\Shared\ESTIMATES\V2025\Team Specific Material\Dissemination\Products\County-Municipios-Metro-Micro Totals\Tables\CO-EST2025-POP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicks\Desktop\NSS\Python\projects\DA17-Capstone\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{244E2BA4-BF96-41B6-ADF9-A2D595143DAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08081E18-9A4B-4282-8A61-C412E72BE940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CO-EST2025-POP-47" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'CO-EST2025-POP-47'!$A$2:$H$106</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'CO-EST2025-POP-47'!$A:$A,'CO-EST2025-POP-47'!$2:$2</definedName>
   </definedNames>
-  <calcPr calcId="0" concurrentCalc="0"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -1792,32 +1792,13 @@
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -1854,13 +1835,32 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2175,48 +2175,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
     </row>
     <row r="2" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
     </row>
     <row r="4" spans="1:8" s="4" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="27"/>
-      <c r="B4" s="31"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="21"/>
       <c r="C4" s="3">
         <v>2020</v>
       </c>
@@ -4733,90 +4733,90 @@
       </c>
     </row>
     <row r="101" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="32" t="s">
+      <c r="A101" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="B101" s="33"/>
-      <c r="C101" s="33"/>
-      <c r="D101" s="33"/>
-      <c r="E101" s="33"/>
-      <c r="F101" s="33"/>
-      <c r="G101" s="33"/>
-      <c r="H101" s="33"/>
+      <c r="B101" s="12"/>
+      <c r="C101" s="12"/>
+      <c r="D101" s="12"/>
+      <c r="E101" s="12"/>
+      <c r="F101" s="12"/>
+      <c r="G101" s="12"/>
+      <c r="H101" s="12"/>
     </row>
     <row r="102" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="11" t="s">
+      <c r="A102" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="B102" s="12"/>
-      <c r="C102" s="12"/>
-      <c r="D102" s="12"/>
-      <c r="E102" s="12"/>
-      <c r="F102" s="12"/>
-      <c r="G102" s="12"/>
-      <c r="H102" s="13"/>
+      <c r="B102" s="23"/>
+      <c r="C102" s="23"/>
+      <c r="D102" s="23"/>
+      <c r="E102" s="23"/>
+      <c r="F102" s="23"/>
+      <c r="G102" s="23"/>
+      <c r="H102" s="24"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" s="14" t="s">
+      <c r="A103" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="B103" s="15"/>
-      <c r="C103" s="15"/>
-      <c r="D103" s="15"/>
-      <c r="E103" s="15"/>
-      <c r="F103" s="15"/>
-      <c r="G103" s="15"/>
-      <c r="H103" s="16"/>
+      <c r="B103" s="26"/>
+      <c r="C103" s="26"/>
+      <c r="D103" s="26"/>
+      <c r="E103" s="26"/>
+      <c r="F103" s="26"/>
+      <c r="G103" s="26"/>
+      <c r="H103" s="27"/>
     </row>
     <row r="104" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="17" t="s">
+      <c r="A104" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="B104" s="18"/>
-      <c r="C104" s="18"/>
-      <c r="D104" s="18"/>
-      <c r="E104" s="18"/>
-      <c r="F104" s="18"/>
-      <c r="G104" s="18"/>
-      <c r="H104" s="19"/>
+      <c r="B104" s="29"/>
+      <c r="C104" s="29"/>
+      <c r="D104" s="29"/>
+      <c r="E104" s="29"/>
+      <c r="F104" s="29"/>
+      <c r="G104" s="29"/>
+      <c r="H104" s="30"/>
     </row>
     <row r="105" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="17" t="s">
+      <c r="A105" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="B105" s="18"/>
-      <c r="C105" s="18"/>
-      <c r="D105" s="18"/>
-      <c r="E105" s="18"/>
-      <c r="F105" s="18"/>
-      <c r="G105" s="18"/>
-      <c r="H105" s="19"/>
+      <c r="B105" s="29"/>
+      <c r="C105" s="29"/>
+      <c r="D105" s="29"/>
+      <c r="E105" s="29"/>
+      <c r="F105" s="29"/>
+      <c r="G105" s="29"/>
+      <c r="H105" s="30"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A106" s="20" t="s">
+      <c r="A106" s="31" t="s">
         <v>105</v>
       </c>
-      <c r="B106" s="21"/>
-      <c r="C106" s="21"/>
-      <c r="D106" s="21"/>
-      <c r="E106" s="21"/>
-      <c r="F106" s="21"/>
-      <c r="G106" s="21"/>
-      <c r="H106" s="22"/>
+      <c r="B106" s="32"/>
+      <c r="C106" s="32"/>
+      <c r="D106" s="32"/>
+      <c r="E106" s="32"/>
+      <c r="F106" s="32"/>
+      <c r="G106" s="32"/>
+      <c r="H106" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A102:H102"/>
+    <mergeCell ref="A103:H103"/>
+    <mergeCell ref="A104:H104"/>
+    <mergeCell ref="A105:H105"/>
+    <mergeCell ref="A106:H106"/>
     <mergeCell ref="A101:H101"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="C3:H3"/>
     <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A102:H102"/>
-    <mergeCell ref="A103:H103"/>
-    <mergeCell ref="A104:H104"/>
-    <mergeCell ref="A105:H105"/>
-    <mergeCell ref="A106:H106"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
